--- a/excel_routes/route_DMM_HMB_threats.xlsx
+++ b/excel_routes/route_DMM_HMB_threats.xlsx
@@ -48,6 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
       </patternFill>
@@ -56,12 +62,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
         <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-432</t>
+          <t>Nesma Airlines NE-155</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1231</v>
+        <v>1140</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1611</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-380</v>
+        <v>-471</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-134</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1409</v>
+        <v>1140</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1611</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-202</v>
+        <v>-471</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>Nile Air NP-134</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -662,7 +662,7 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1140</v>
+        <v>1119</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1845</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-705</v>
+        <v>-726</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1146</v>
+        <v>1230</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1845</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-699</v>
+        <v>-615</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,7 +752,7 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -776,28 +776,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-854</t>
+          <t>Nile Air NP-234</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1469</v>
+        <v>1409</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1845</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-376</v>
+        <v>-436</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -828,10 +828,10 @@
         <v>615</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-253</v>
+        <v>-343</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,7 +842,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>Nile Air NP-134</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>615</v>
+        <v>679</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-343</v>
+        <v>-279</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,28 +911,28 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>827</v>
+        <v>679</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-131</v>
+        <v>-279</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -956,28 +956,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>835</v>
+        <v>615</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-123</v>
+        <v>-343</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,28 +1001,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-155</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>615</v>
+        <v>827</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-253</v>
+        <v>-131</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,28 +1046,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>629</v>
+        <v>835</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-239</v>
+        <v>-123</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>Nesma Airlines NE-155</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>868</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-239</v>
+        <v>-253</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1112,7 +1112,7 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-234</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>771</v>
+        <v>629</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1198</v>
+        <v>868</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-427</v>
+        <v>-239</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-854</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>771</v>
+        <v>629</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1198</v>
+        <v>868</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-427</v>
+        <v>-239</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1202,57 +1202,12 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15-JUN-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-332</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>914</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>1198</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-284</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_DMM_HMB_threats.xlsx
+++ b/excel_routes/route_DMM_HMB_threats.xlsx
@@ -48,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -60,8 +60,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-155</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1140</v>
+        <v>1230</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1611</v>
+        <v>1845</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-471</v>
+        <v>-615</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>Nile Air NP-234</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1140</v>
+        <v>1231</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1611</v>
+        <v>1845</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-471</v>
+        <v>-614</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-134</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1409</v>
+        <v>1231</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1611</v>
+        <v>1845</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-202</v>
+        <v>-614</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1119</v>
+        <v>615</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1845</v>
+        <v>868</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-726</v>
+        <v>-253</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1230</v>
+        <v>615</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1845</v>
+        <v>958</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-615</v>
+        <v>-343</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1409</v>
+        <v>827</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1845</v>
+        <v>958</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-436</v>
+        <v>-131</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>615</v>
+        <v>835</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-343</v>
+        <v>-123</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-134</t>
+          <t>Nesma Airlines NE-155</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>679</v>
+        <v>615</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>958</v>
+        <v>868</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-279</v>
+        <v>-253</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>Nile Air NP-134</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>679</v>
+        <v>629</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>958</v>
+        <v>868</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-279</v>
+        <v>-239</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>Nile Air NP-234</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>615</v>
+        <v>629</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>958</v>
+        <v>868</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-343</v>
+        <v>-239</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,26 +1001,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>827</v>
+        <v>723</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-131</v>
+        <v>-235</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-155</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>615</v>
+        <v>932</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-253</v>
+        <v>-26</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>629</v>
+        <v>679</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-239</v>
+        <v>-279</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,33 +1181,1428 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>EgyptAir MS-688</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>958</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-203</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>20-JUL-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>827</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>958</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-131</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>27-JUL-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-1289</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>27-JUL-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>27-JUL-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-1059</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>Nile Air NP-232</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D21" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-1059</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-682</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>827</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-911</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-688</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-903</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-684</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>611</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-1127</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
         <v>629</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>868</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-239</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
+      <c r="E26" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>17-AUG-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>17-AUG-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-684</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>611</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-1127</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>17-AUG-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-684</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>611</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-1127</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-232</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-1059</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-1369</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-688</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-983</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>31-AUG-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-1369</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>31-AUG-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>31-AUG-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-1369</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-684</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>611</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-1127</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-232</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-684</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>611</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-1127</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-232</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_DMM_HMB_threats.xlsx
+++ b/excel_routes/route_DMM_HMB_threats.xlsx
@@ -465,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -558,10 +558,10 @@
         <v>1230</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1845</v>
+        <v>2157</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-615</v>
+        <v>-927</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -603,10 +603,10 @@
         <v>1231</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1845</v>
+        <v>2157</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-614</v>
+        <v>-926</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -648,10 +648,10 @@
         <v>1231</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1845</v>
+        <v>2157</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-614</v>
+        <v>-926</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -693,10 +693,10 @@
         <v>615</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-253</v>
+        <v>-343</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>615</v>
+        <v>827</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-343</v>
+        <v>-131</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-131</v>
+        <v>-123</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>Nesma Airlines NE-155</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>835</v>
+        <v>615</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>958</v>
+        <v>868</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-123</v>
+        <v>-253</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-155</t>
+          <t>Nile Air NP-234</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>615</v>
+        <v>629</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>868</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-253</v>
+        <v>-239</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -911,7 +911,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-134</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>Air Arabia Egypt E5-316</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>629</v>
+        <v>975</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>868</v>
+        <v>1498</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-239</v>
+        <v>-523</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>flyadeal F3-324</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>723</v>
+        <v>1095</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>958</v>
+        <v>1498</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-235</v>
+        <v>-403</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>Nile Air NP-234</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>835</v>
+        <v>1143</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>958</v>
+        <v>1498</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-123</v>
+        <v>-355</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-682</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>679</v>
+        <v>932</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-279</v>
+        <v>-26</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>755</v>
+        <v>932</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-203</v>
+        <v>-26</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>827</v>
+        <v>723</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-131</v>
+        <v>-235</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>449</v>
+        <v>835</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-1289</v>
+        <v>-123</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>569</v>
+        <v>932</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1169</v>
+        <v>-26</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>679</v>
+        <v>743</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-1059</v>
+        <v>-215</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>679</v>
+        <v>755</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-1059</v>
+        <v>-203</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-682</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>827</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-911</v>
+        <v>-131</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>835</v>
+        <v>569</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-903</v>
+        <v>-1169</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>569</v>
+        <v>611</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-1169</v>
+        <v>-1127</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>23</v>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>611</v>
+        <v>679</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1127</v>
+        <v>-1059</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>629</v>
+        <v>703</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-1109</v>
+        <v>-1035</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>569</v>
+        <v>827</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-1169</v>
+        <v>-911</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,26 +1721,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>611</v>
+        <v>835</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-1127</v>
+        <v>-903</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,26 +1766,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>629</v>
+        <v>569</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-1109</v>
+        <v>-1169</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>569</v>
+        <v>629</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-1169</v>
+        <v>-1109</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1860,22 +1860,22 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>611</v>
+        <v>671</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-1127</v>
+        <v>-1067</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>679</v>
+        <v>429</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1059</v>
+        <v>-1309</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>369</v>
+        <v>569</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1369</v>
+        <v>-1169</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,26 +1991,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>389</v>
+        <v>629</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-1349</v>
+        <v>-1109</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,26 +2036,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>755</v>
+        <v>389</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-983</v>
+        <v>-1349</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>31-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2085,22 +2085,22 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>369</v>
+        <v>623</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1369</v>
+        <v>-1115</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>31-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>389</v>
+        <v>629</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-1349</v>
+        <v>-1109</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>31-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,26 +2171,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>629</v>
+        <v>569</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-1109</v>
+        <v>-1169</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>369</v>
+        <v>629</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-1369</v>
+        <v>-1109</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>569</v>
+        <v>755</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1169</v>
+        <v>-983</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>629</v>
+        <v>389</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-1109</v>
+        <v>-1349</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,26 +2351,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-1169</v>
+        <v>-1145</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>611</v>
+        <v>629</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-1127</v>
+        <v>-1109</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>629</v>
+        <v>569</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-1109</v>
+        <v>-1169</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-1169</v>
+        <v>-1145</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>611</v>
+        <v>679</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-1127</v>
+        <v>-1059</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>24-AUG-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,33 +2576,798 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-1369</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>24-AUG-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>24-AUG-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-1369</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-688</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-983</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>31-AUG-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>31-AUG-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-1175</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>31-AUG-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-684</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>611</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-1127</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
           <t>Nile Air NP-232</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D58" s="2" t="n">
         <v>629</v>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F47" s="2" t="n">
+      <c r="E58" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F58" s="2" t="n">
         <v>-1109</v>
       </c>
-      <c r="G47" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I47" s="2" t="n">
+      <c r="G58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-1369</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-1175</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_DMM_HMB_threats.xlsx
+++ b/excel_routes/route_DMM_HMB_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>827</v>
+        <v>679</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-131</v>
+        <v>-279</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>Nile Air NP-134</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>835</v>
+        <v>679</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-123</v>
+        <v>-279</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-155</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>615</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-253</v>
+        <v>-343</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>629</v>
+        <v>827</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-239</v>
+        <v>-131</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>629</v>
+        <v>835</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-239</v>
+        <v>-123</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-316</t>
+          <t>Nesma Airlines NE-155</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>975</v>
+        <v>615</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1498</v>
+        <v>868</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-523</v>
+        <v>-253</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-324</t>
+          <t>Nile Air NP-234</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1095</v>
+        <v>629</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1498</v>
+        <v>868</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-403</v>
+        <v>-239</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1143</v>
+        <v>629</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1498</v>
+        <v>868</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-355</v>
+        <v>-239</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>Air Arabia Egypt E5-316</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>932</v>
+        <v>975</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>958</v>
+        <v>1498</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-26</v>
+        <v>-523</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-682</t>
+          <t>flyadeal F3-324</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>932</v>
+        <v>1095</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>958</v>
+        <v>1498</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-26</v>
+        <v>-403</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>932</v>
+        <v>1203</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>958</v>
+        <v>1498</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-26</v>
+        <v>-295</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>flyadeal F3-324</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>723</v>
+        <v>1095</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>958</v>
+        <v>1318</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-235</v>
+        <v>-223</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>835</v>
+        <v>932</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-123</v>
+        <v>-26</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>743</v>
+        <v>932</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-215</v>
+        <v>-26</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>755</v>
+        <v>835</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-203</v>
+        <v>-123</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1427,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>827</v>
+        <v>863</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-131</v>
+        <v>-95</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,30 +1496,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>569</v>
+        <v>932</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1169</v>
+        <v>-26</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>611</v>
+        <v>743</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-1127</v>
+        <v>-215</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>679</v>
+        <v>755</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1059</v>
+        <v>-203</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>703</v>
+        <v>827</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-1035</v>
+        <v>-131</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-682</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>827</v>
+        <v>743</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-911</v>
+        <v>-995</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-903</v>
+        <v>-911</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46</v>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1770,22 +1770,22 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>569</v>
+        <v>827</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-1169</v>
+        <v>-911</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>629</v>
+        <v>569</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-1109</v>
+        <v>-1169</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,26 +1856,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>671</v>
+        <v>626</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-1067</v>
+        <v>-1112</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1905,22 +1905,22 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>429</v>
+        <v>663</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1309</v>
+        <v>-1075</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>569</v>
+        <v>679</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1169</v>
+        <v>-1059</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,26 +1991,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>629</v>
+        <v>827</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-1109</v>
+        <v>-911</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,26 +2036,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>389</v>
+        <v>835</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-1349</v>
+        <v>-903</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2085,22 +2085,22 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>623</v>
+        <v>429</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1115</v>
+        <v>-1309</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,26 +2171,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>569</v>
+        <v>671</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-1169</v>
+        <v>-1067</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>629</v>
+        <v>429</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-1109</v>
+        <v>-1309</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>755</v>
+        <v>569</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-983</v>
+        <v>-1169</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>389</v>
+        <v>629</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-1349</v>
+        <v>-1109</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,26 +2351,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-1145</v>
+        <v>-1172</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-1109</v>
+        <v>-1115</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>569</v>
+        <v>629</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-1169</v>
+        <v>-1109</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>593</v>
+        <v>419</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-1145</v>
+        <v>-1319</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>679</v>
+        <v>629</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-1059</v>
+        <v>-1109</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>30</v>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>24-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,26 +2576,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>369</v>
+        <v>755</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-1369</v>
+        <v>-983</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>24-AUG-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2625,22 +2625,22 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>389</v>
+        <v>566</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-1349</v>
+        <v>-1172</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>24-AUG-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,26 +2666,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>629</v>
+        <v>593</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-1109</v>
+        <v>-1145</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>369</v>
+        <v>629</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-1369</v>
+        <v>-1109</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,26 +2756,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>569</v>
+        <v>389</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-1169</v>
+        <v>-1349</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,26 +2801,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>755</v>
+        <v>399</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-983</v>
+        <v>-1339</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>31-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,26 +2846,26 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>389</v>
+        <v>569</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-1349</v>
+        <v>-1169</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31-AUG-26</t>
+          <t>24-AUG-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31-AUG-26</t>
+          <t>24-AUG-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>629</v>
+        <v>566</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-1109</v>
+        <v>-1172</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>30</v>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>24-AUG-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,26 +2981,26 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>569</v>
+        <v>629</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-1169</v>
+        <v>-1109</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,26 +3026,26 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>611</v>
+        <v>389</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-1127</v>
+        <v>-1349</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,26 +3071,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>629</v>
+        <v>563</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-1109</v>
+        <v>-1175</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,26 +3116,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>369</v>
+        <v>755</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-1369</v>
+        <v>-983</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>31-AUG-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,26 +3161,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>389</v>
+        <v>563</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-1349</v>
+        <v>-1175</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>31-AUG-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>629</v>
+        <v>566</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-1109</v>
+        <v>-1172</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>30</v>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>31-AUG-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,26 +3251,26 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>389</v>
+        <v>629</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-1349</v>
+        <v>-1109</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,26 +3296,26 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>563</v>
+        <v>389</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-1175</v>
+        <v>-1349</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -3331,43 +3331,673 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-1309</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-232</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-1369</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-1369</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-232</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
           <t>14-SEP-26</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-1369</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Nile Air NP-332</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D74" s="2" t="n">
         <v>629</v>
       </c>
-      <c r="E64" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F64" s="2" t="n">
+      <c r="E74" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F74" s="2" t="n">
         <v>-1109</v>
       </c>
-      <c r="G64" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I64" s="2" t="n">
+      <c r="G74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>593</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-1145</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>596</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-1142</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-232</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>28-SEP-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>778</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-215</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_DMM_HMB_threats.xlsx
+++ b/excel_routes/route_DMM_HMB_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-234</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1203</v>
+        <v>1143</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1498</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-295</v>
+        <v>-355</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>743</v>
+        <v>679</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-215</v>
+        <v>-279</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>743</v>
+        <v>827</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-995</v>
+        <v>-911</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-682</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>827</v>
+        <v>869</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-911</v>
+        <v>-869</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>46</v>
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>679</v>
+        <v>743</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1059</v>
+        <v>-995</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-1309</v>
+        <v>-1349</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>15</v>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>569</v>
+        <v>429</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1169</v>
+        <v>-1309</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,26 +2351,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>566</v>
+        <v>623</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-1172</v>
+        <v>-1115</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-1115</v>
+        <v>-1109</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>629</v>
+        <v>755</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-1109</v>
+        <v>-983</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-1319</v>
+        <v>-1349</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>15</v>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>629</v>
+        <v>399</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-1109</v>
+        <v>-1339</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,26 +2576,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>755</v>
+        <v>629</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-983</v>
+        <v>-1109</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2625,22 +2625,22 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>566</v>
+        <v>389</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-1172</v>
+        <v>-1349</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2670,22 +2670,22 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>593</v>
+        <v>399</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-1145</v>
+        <v>-1339</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>629</v>
+        <v>569</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-1109</v>
+        <v>-1169</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>31-AUG-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-1349</v>
+        <v>-1369</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>15</v>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>31-AUG-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-1339</v>
+        <v>-1349</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>15</v>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>31-AUG-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,26 +2846,26 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>569</v>
+        <v>629</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-1169</v>
+        <v>-1109</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>24-AUG-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,26 +2891,26 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-1175</v>
+        <v>-1169</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>24-AUG-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,26 +2936,26 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>566</v>
+        <v>611</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-1172</v>
+        <v>-1127</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24-AUG-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,26 +3026,26 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>389</v>
+        <v>569</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-1349</v>
+        <v>-1169</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,26 +3071,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>563</v>
+        <v>611</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-1175</v>
+        <v>-1127</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,26 +3116,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>755</v>
+        <v>629</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-983</v>
+        <v>-1109</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>31-AUG-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,26 +3161,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-1175</v>
+        <v>-1169</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>31-AUG-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,26 +3206,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>566</v>
+        <v>611</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-1172</v>
+        <v>-1127</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>31-AUG-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -3278,726 +3278,6 @@
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>04-SEP-26</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-911</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>389</v>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>-1349</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>04-SEP-26</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-894</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>-1309</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>04-SEP-26</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-232</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>629</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>-1109</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>07-SEP-26</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-894</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="n">
-        <v>369</v>
-      </c>
-      <c r="E66" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>-1369</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>07-SEP-26</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-911</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="n">
-        <v>389</v>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>-1349</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>07-SEP-26</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-332</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>629</v>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>-1109</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-894</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>369</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>-1369</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-911</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>389</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>-1349</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-232</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="n">
-        <v>629</v>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>-1109</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>14-SEP-26</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-894</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>369</v>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>-1369</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>14-SEP-26</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-911</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="n">
-        <v>389</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>-1349</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>14-SEP-26</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-332</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>629</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>-1109</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-894</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="n">
-        <v>593</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>-1145</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-911</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>596</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>-1142</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-232</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>629</v>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>-1109</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>28-SEP-26</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-894</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>563</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>778</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>-215</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_DMM_HMB_threats.xlsx
+++ b/excel_routes/route_DMM_HMB_threats.xlsx
@@ -48,12 +48,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
       </patternFill>
@@ -62,6 +56,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1230</v>
+        <v>409</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2157</v>
+        <v>628</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-927</v>
+        <v>-219</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>Nesma Airlines NE-155</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1231</v>
+        <v>410</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2157</v>
+        <v>628</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-926</v>
+        <v>-218</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>flyadeal F3-324</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1231</v>
+        <v>958</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2157</v>
+        <v>1498</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-926</v>
+        <v>-540</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,28 +686,28 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>Air Arabia Egypt E5-316</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>615</v>
+        <v>1051</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>958</v>
+        <v>1498</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-343</v>
+        <v>-447</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>679</v>
+        <v>1143</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>958</v>
+        <v>1498</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-279</v>
+        <v>-355</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,7 +752,7 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-134</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>679</v>
+        <v>723</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-279</v>
+        <v>-235</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,7 +797,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,28 +821,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>615</v>
+        <v>872</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-343</v>
+        <v>-86</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>827</v>
+        <v>969</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-131</v>
+        <v>11</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -887,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>835</v>
+        <v>708</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>958</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-123</v>
+        <v>-250</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-155</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>615</v>
+        <v>792</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-253</v>
+        <v>-166</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,28 +1001,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>629</v>
+        <v>864</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-239</v>
+        <v>-94</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>629</v>
+        <v>864</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>868</v>
+        <v>1738</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-239</v>
+        <v>-874</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-316</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>975</v>
+        <v>864</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1498</v>
+        <v>1738</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-523</v>
+        <v>-874</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-324</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1095</v>
+        <v>906</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1498</v>
+        <v>1738</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-403</v>
+        <v>-832</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1143</v>
+        <v>449</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1498</v>
+        <v>1738</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-355</v>
+        <v>-1289</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-324</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1095</v>
+        <v>606</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1318</v>
+        <v>1738</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-223</v>
+        <v>-1132</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>932</v>
+        <v>679</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>958</v>
+        <v>1738</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-26</v>
+        <v>-1059</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-682</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>932</v>
+        <v>629</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>958</v>
+        <v>1738</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-26</v>
+        <v>-1109</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>932</v>
+        <v>638</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>958</v>
+        <v>1738</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-26</v>
+        <v>-1100</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>835</v>
+        <v>906</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>958</v>
+        <v>1738</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-123</v>
+        <v>-832</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1427,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,30 +1451,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>863</v>
+        <v>606</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>958</v>
+        <v>1738</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-95</v>
+        <v>-1132</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,30 +1496,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-682</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>932</v>
+        <v>629</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>958</v>
+        <v>1738</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-26</v>
+        <v>-1109</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>679</v>
+        <v>648</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>958</v>
+        <v>1738</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-279</v>
+        <v>-1090</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>755</v>
+        <v>389</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>958</v>
+        <v>1738</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-203</v>
+        <v>-1349</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>827</v>
+        <v>414</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>958</v>
+        <v>1738</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-131</v>
+        <v>-1324</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,28 +1676,28 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-682</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>827</v>
+        <v>629</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-911</v>
+        <v>-1109</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,28 +1721,28 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>827</v>
+        <v>389</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-911</v>
+        <v>-1349</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,28 +1766,28 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>869</v>
+        <v>414</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-869</v>
+        <v>-1324</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,28 +1811,28 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>569</v>
+        <v>679</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-1169</v>
+        <v>-1059</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1860,13 +1860,13 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>626</v>
+        <v>596</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-1112</v>
+        <v>-1142</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
@@ -1877,7 +1877,7 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>663</v>
+        <v>608</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1075</v>
+        <v>-1130</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>40</v>
@@ -1922,7 +1922,7 @@
       <c r="I32" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,28 +1946,28 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>743</v>
+        <v>679</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-995</v>
+        <v>-1059</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,28 +1991,28 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-682</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>827</v>
+        <v>384</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-911</v>
+        <v>-1354</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,28 +2036,28 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>835</v>
+        <v>389</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-903</v>
+        <v>-1349</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,28 +2081,28 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>429</v>
+        <v>629</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1309</v>
+        <v>-1109</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,28 +2126,28 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>629</v>
+        <v>384</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-1109</v>
+        <v>-1354</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,28 +2171,28 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>671</v>
+        <v>389</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-1067</v>
+        <v>-1349</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,28 +2216,28 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>389</v>
+        <v>629</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-1349</v>
+        <v>-1109</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1309</v>
+        <v>-1354</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>15</v>
@@ -2282,7 +2282,7 @@
       <c r="I40" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,28 +2306,28 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>629</v>
+        <v>389</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-1109</v>
+        <v>-1349</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,933 +2351,33 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-1115</v>
+        <v>-1109</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>14-AUG-26</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-232</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>629</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>-1109</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>14-AUG-26</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-688</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>755</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>-983</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>17-AUG-26</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-911</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>389</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>-1349</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>17-AUG-26</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-894</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>399</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>-1339</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>17-AUG-26</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-332</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>629</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>-1109</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>21-AUG-26</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-911</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>389</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>-1349</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>21-AUG-26</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-894</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>399</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>-1339</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>21-AUG-26</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-698</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>569</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>-1169</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>31-AUG-26</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-894</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>369</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>-1369</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>31-AUG-26</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-911</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>389</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>-1349</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>31-AUG-26</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-332</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>629</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>-1109</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>07-SEP-26</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-698</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>569</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>-1169</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>07-SEP-26</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-684</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>611</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>-1127</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>07-SEP-26</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-332</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>629</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>-1109</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-698</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>569</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>-1169</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-684</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>611</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>-1127</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-232</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>629</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>-1109</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-698</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>569</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>-1169</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-684</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>611</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>-1127</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-232</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>629</v>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>-1109</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_DMM_HMB_threats.xlsx
+++ b/excel_routes/route_DMM_HMB_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>Nile Air NP-234</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -564,13 +564,13 @@
         <v>-219</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-155</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>628</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-218</v>
+        <v>-219</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-324</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>958</v>
+        <v>409</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1498</v>
+        <v>568</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-540</v>
+        <v>-159</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-316</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1051</v>
+        <v>974</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1498</v>
+        <v>958</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-447</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1143</v>
+        <v>982</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1498</v>
+        <v>958</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-355</v>
+        <v>24</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>958</v>
+        <v>868</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-235</v>
+        <v>-135</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>872</v>
+        <v>733</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>958</v>
+        <v>868</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-86</v>
+        <v>-135</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-682</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>969</v>
+        <v>733</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>958</v>
+        <v>868</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>11</v>
+        <v>-135</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>708</v>
+        <v>678</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>958</v>
+        <v>1078</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-250</v>
+        <v>-400</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>792</v>
+        <v>733</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>958</v>
+        <v>1078</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-166</v>
+        <v>-345</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -977,7 +977,7 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>864</v>
+        <v>775</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>958</v>
+        <v>1078</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-94</v>
+        <v>-303</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-682</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>864</v>
+        <v>670</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-874</v>
+        <v>-288</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>864</v>
+        <v>670</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-874</v>
+        <v>-288</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>906</v>
+        <v>712</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1738</v>
+        <v>958</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-832</v>
+        <v>-246</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,28 +1181,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>449</v>
+        <v>670</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1289</v>
+        <v>-1068</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1230,24 +1230,24 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>606</v>
+        <v>670</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-1132</v>
+        <v>-1068</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,28 +1271,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>679</v>
+        <v>775</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-1059</v>
+        <v>-963</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,28 +1316,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>629</v>
+        <v>515</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1109</v>
+        <v>-1223</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,28 +1361,28 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>638</v>
+        <v>515</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-1100</v>
+        <v>-1223</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,28 +1406,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>906</v>
+        <v>515</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-832</v>
+        <v>-1223</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,28 +1451,28 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>606</v>
+        <v>678</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1132</v>
+        <v>-1060</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,28 +1496,28 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>629</v>
+        <v>733</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1109</v>
+        <v>-1005</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,28 +1541,28 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>648</v>
+        <v>733</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-1090</v>
+        <v>-1005</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,28 +1586,28 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>389</v>
+        <v>569</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1349</v>
+        <v>-1169</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,28 +1631,28 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>414</v>
+        <v>629</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-1324</v>
+        <v>-1109</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>17-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,28 +1676,28 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>629</v>
+        <v>869</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-1109</v>
+        <v>-869</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>389</v>
+        <v>489</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-1349</v>
+        <v>-1249</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>15</v>
@@ -1742,7 +1742,7 @@
       <c r="I28" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,28 +1766,28 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>414</v>
+        <v>569</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-1324</v>
+        <v>-1169</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>679</v>
+        <v>629</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-1059</v>
+        <v>-1109</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>30</v>
@@ -1832,7 +1832,7 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1860,13 +1860,13 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>596</v>
+        <v>566</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-1142</v>
+        <v>-1172</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
@@ -1877,7 +1877,7 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,28 +1901,28 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1130</v>
+        <v>-1109</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,28 +1946,28 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>679</v>
+        <v>643</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1059</v>
+        <v>-1095</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,28 +1991,28 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>384</v>
+        <v>626</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-1354</v>
+        <v>-1112</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,28 +2036,28 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>389</v>
+        <v>629</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-1349</v>
+        <v>-1109</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,28 +2081,28 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>629</v>
+        <v>643</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1109</v>
+        <v>-1095</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,28 +2126,28 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>384</v>
+        <v>566</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-1354</v>
+        <v>-1172</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,28 +2171,28 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>389</v>
+        <v>613</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-1349</v>
+        <v>-1125</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>17-AUG-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -2237,7 +2237,7 @@
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1354</v>
+        <v>-1319</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>15</v>
@@ -2282,7 +2282,7 @@
       <c r="I40" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2310,24 +2310,24 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>389</v>
+        <v>566</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>1738</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-1349</v>
+        <v>-1172</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2341,43 +2341,988 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>24-AUG-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>566</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-1172</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>24-AUG-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>583</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-1155</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>24-AUG-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>419</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-1319</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>419</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-1319</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>31-AUG-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>31-AUG-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>613</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-1125</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>31-AUG-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>419</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-1319</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-232</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>643</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-1095</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>583</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-1155</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-1109</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>566</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-1172</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>583</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-1155</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-316</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>940</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-798</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
           <t>14-SEP-26</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>SM-438</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-438</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Nile Air NP-332</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D63" s="2" t="n">
         <v>629</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F42" s="2" t="n">
+      <c r="E63" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F63" s="2" t="n">
         <v>-1109</v>
       </c>
-      <c r="G42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" s="2" t="n">
+      <c r="G63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
